--- a/Accounting-Analytics-Textbook/Unit 1/data/Stock data.xlsx
+++ b/Accounting-Analytics-Textbook/Unit 1/data/Stock data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f27c7dfe41a57d57/Texas State/ACC 3323/Lecture slides/By Topic/Unit 1 - Process of Analytics/1-01 Process of Analytics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://txst-my.sharepoint.com/personal/mih53_txstate_edu/Documents/ACC 3323/Lecture slides/By Topic/Unit 1 - Process of Analytics/1-2 Process of Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{B0E36721-B4B8-4F10-AC82-99A769EA0A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A996F0F1-2DB4-4BA5-B625-8C23A85CDFEC}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{B0E36721-B4B8-4F10-AC82-99A769EA0A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DF04852-37ED-4C4D-B8DD-88235C023E9D}"/>
   <bookViews>
-    <workbookView xWindow="25305" yWindow="0" windowWidth="22215" windowHeight="17280" xr2:uid="{67D4CAEA-468E-42DE-B9D9-DCB552137511}"/>
+    <workbookView xWindow="9600" yWindow="0" windowWidth="19410" windowHeight="17280" xr2:uid="{67D4CAEA-468E-42DE-B9D9-DCB552137511}"/>
   </bookViews>
   <sheets>
-    <sheet name="XOM" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId1"/>
+    <sheet name="With returns and pivot table" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="8" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="10">
   <si>
     <t>Date</t>
   </si>
@@ -58,13 +62,22 @@
   <si>
     <t>Closing Price</t>
   </si>
+  <si>
+    <t>Daily Return</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Avg. Daily Return</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -77,21 +90,39 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -99,48 +130,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="42" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="42" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -153,26 +207,155 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Vic Anand" refreshedDate="46256.625138773146" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="9" xr:uid="{B9B78189-BAEF-4B0C-A9C5-2DD217E6AD61}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E10" sheet="With returns and pivot table"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Ticker" numFmtId="0">
+      <sharedItems count="3">
+        <s v="DELL"/>
+        <s v="TXN"/>
+        <s v="XOM"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-08-20T00:00:00" maxDate="2025-08-23T00:00:00"/>
+    </cacheField>
+    <cacheField name="Closing Price" numFmtId="42">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="250"/>
+    </cacheField>
+    <cacheField name="Yesterday's Closing Price" numFmtId="42">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="250"/>
+    </cacheField>
+    <cacheField name="Daily Return" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.2" maxValue="0.25"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E0BFB534-A57A-4767-92B6-A8AD23EDC36A}" name="Table1" displayName="Table1" ref="A1:D10" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:D10" xr:uid="{E0BFB534-A57A-4767-92B6-A8AD23EDC36A}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4CDA6415-32A0-4348-9945-1531F3AA90E4}" name="Ticker"/>
-    <tableColumn id="2" xr3:uid="{CCD73C56-ED58-46A2-B23F-5B889648F6DE}" name="Date" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{7A829373-F6A7-455C-819C-767183440847}" name="Closing Price" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{3A1F607E-E879-407F-9CCD-B1407FC48B7A}" name="Yesterday's Closing Price" dataDxfId="1"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="9">
+  <r>
+    <x v="0"/>
+    <d v="2025-08-20T00:00:00"/>
+    <n v="100"/>
+    <n v="80"/>
+    <n v="0.25"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <d v="2025-08-21T00:00:00"/>
+    <n v="80"/>
+    <n v="100"/>
+    <n v="-0.2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <d v="2025-08-22T00:00:00"/>
+    <n v="100"/>
+    <n v="80"/>
+    <n v="0.25"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <d v="2025-08-20T00:00:00"/>
+    <n v="250"/>
+    <n v="200"/>
+    <n v="0.25"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <d v="2025-08-21T00:00:00"/>
+    <n v="200"/>
+    <n v="250"/>
+    <n v="-0.2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <d v="2025-08-22T00:00:00"/>
+    <n v="220"/>
+    <n v="200"/>
+    <n v="0.1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <d v="2025-08-20T00:00:00"/>
+    <n v="100"/>
+    <n v="125"/>
+    <n v="-0.2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <d v="2025-08-21T00:00:00"/>
+    <n v="110"/>
+    <n v="100"/>
+    <n v="0.1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <d v="2025-08-22T00:00:00"/>
+    <n v="121"/>
+    <n v="110"/>
+    <n v="0.1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD26A1AC-783F-4C56-ACF7-AE4050F772EC}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C13:D16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="42" showAll="0"/>
+    <pivotField numFmtId="42" showAll="0"/>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Avg. Daily Return" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -492,152 +675,159 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A495C3-1D73-47E5-9D39-1E319D07CEE4}">
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="7">
         <v>45889</v>
       </c>
-      <c r="C2" s="3">
-        <v>128.47999999999999</v>
-      </c>
-      <c r="D2" s="3">
-        <v>135.19999999999999</v>
+      <c r="C2" s="12">
+        <v>100</v>
+      </c>
+      <c r="D2" s="12">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>45889</v>
-      </c>
-      <c r="C3" s="3">
-        <v>200.77</v>
-      </c>
-      <c r="D3" s="3">
-        <v>195.94</v>
+        <v>45890</v>
+      </c>
+      <c r="C3" s="13">
+        <v>80</v>
+      </c>
+      <c r="D3" s="13">
+        <f>C2</f>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>45889</v>
-      </c>
-      <c r="C4" s="3">
-        <v>108.53</v>
-      </c>
-      <c r="D4" s="3">
-        <v>107.42</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8">
+        <v>45891</v>
+      </c>
+      <c r="C4" s="14">
+        <v>100</v>
+      </c>
+      <c r="D4" s="14">
+        <f>C3</f>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
+        <v>45889</v>
+      </c>
+      <c r="C5" s="13">
+        <v>250</v>
+      </c>
+      <c r="D5" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8">
         <v>45890</v>
       </c>
-      <c r="C5" s="3">
-        <v>127.83</v>
-      </c>
-      <c r="D5" s="3">
-        <v>128.47999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <v>45890</v>
-      </c>
-      <c r="C6" s="3">
-        <v>200.71</v>
-      </c>
-      <c r="D6" s="3">
-        <v>200.77</v>
+      <c r="C6" s="14">
+        <v>200</v>
+      </c>
+      <c r="D6" s="14">
+        <f>C5</f>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45891</v>
+      </c>
+      <c r="C7" s="13">
+        <v>220</v>
+      </c>
+      <c r="D7" s="13">
+        <f>C6</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1">
-        <v>45890</v>
-      </c>
-      <c r="C7" s="3">
-        <v>109.23</v>
-      </c>
-      <c r="D7" s="3">
-        <v>108.53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>45891</v>
-      </c>
-      <c r="C8" s="3">
-        <v>130.84</v>
-      </c>
-      <c r="D8" s="3">
-        <v>127.83</v>
+      <c r="B8" s="8">
+        <v>45889</v>
+      </c>
+      <c r="C8" s="14">
+        <v>100</v>
+      </c>
+      <c r="D8" s="14">
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1">
+        <v>45890</v>
+      </c>
+      <c r="C9" s="13">
+        <v>110</v>
+      </c>
+      <c r="D9" s="13">
+        <f>C8</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9">
         <v>45891</v>
       </c>
-      <c r="C9" s="3">
-        <v>206.06</v>
-      </c>
-      <c r="D9" s="3">
-        <v>200.71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1">
-        <v>45891</v>
-      </c>
-      <c r="C10" s="3">
-        <v>111.28</v>
-      </c>
-      <c r="D10" s="3">
-        <v>109.23</v>
+      <c r="C10" s="15">
+        <v>121</v>
+      </c>
+      <c r="D10" s="15">
+        <f>C9</f>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1318,55 +1508,10 @@
     <row r="236" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B236" s="1"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B237" s="1"/>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B238" s="1"/>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B239" s="1"/>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B240" s="1"/>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B241" s="1"/>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B242" s="1"/>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B243" s="1"/>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B244" s="1"/>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B245" s="1"/>
-    </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B246" s="1"/>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B247" s="1"/>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B248" s="1"/>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B249" s="1"/>
-    </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B250" s="1"/>
-    </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B251" s="1"/>
-    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D10">
+    <sortCondition ref="A2:A10"/>
     <sortCondition ref="B2:B10"/>
-    <sortCondition ref="A2:A10"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1374,8 +1519,920 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;"+,Bold"&amp;18Stock Price Data</oddHeader>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DCEEB4-996E-44AC-876E-067E433CDB27}">
+  <dimension ref="A1:E236"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C2" s="12">
+        <v>100</v>
+      </c>
+      <c r="D2" s="12">
+        <v>80</v>
+      </c>
+      <c r="E2" s="17">
+        <f>(C2-D2)/D2</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45890</v>
+      </c>
+      <c r="C3" s="13">
+        <v>80</v>
+      </c>
+      <c r="D3" s="13">
+        <f>C2</f>
+        <v>100</v>
+      </c>
+      <c r="E3" s="16">
+        <f t="shared" ref="E3:E10" si="0">(C3-D3)/D3</f>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8">
+        <v>45891</v>
+      </c>
+      <c r="C4" s="14">
+        <v>100</v>
+      </c>
+      <c r="D4" s="14">
+        <f>C3</f>
+        <v>80</v>
+      </c>
+      <c r="E4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>45889</v>
+      </c>
+      <c r="C5" s="13">
+        <v>250</v>
+      </c>
+      <c r="D5" s="13">
+        <v>200</v>
+      </c>
+      <c r="E5" s="16">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8">
+        <v>45890</v>
+      </c>
+      <c r="C6" s="14">
+        <v>200</v>
+      </c>
+      <c r="D6" s="14">
+        <f>C5</f>
+        <v>250</v>
+      </c>
+      <c r="E6" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45891</v>
+      </c>
+      <c r="C7" s="13">
+        <v>220</v>
+      </c>
+      <c r="D7" s="13">
+        <f>C6</f>
+        <v>200</v>
+      </c>
+      <c r="E7" s="16">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8">
+        <v>45889</v>
+      </c>
+      <c r="C8" s="14">
+        <v>100</v>
+      </c>
+      <c r="D8" s="14">
+        <v>125</v>
+      </c>
+      <c r="E8" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45890</v>
+      </c>
+      <c r="C9" s="13">
+        <v>110</v>
+      </c>
+      <c r="D9" s="13">
+        <f>C8</f>
+        <v>100</v>
+      </c>
+      <c r="E9" s="16">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="9">
+        <v>45891</v>
+      </c>
+      <c r="C10" s="15">
+        <v>121</v>
+      </c>
+      <c r="D10" s="15">
+        <f>C9</f>
+        <v>110</v>
+      </c>
+      <c r="E10" s="18">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="16">
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4.9999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="1"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="1"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="1"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="1"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="1"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="1"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="1"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="1"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="1"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="1"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="1"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="1"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="1"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="1"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="1"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="1"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="1"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="1"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="1"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="1"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="1"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="1"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="1"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="1"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="1"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="1"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="1"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="1"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="1"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="1"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="1"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="1"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="1"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="1"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="1"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="1"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="1"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="1"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="1"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="1"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="1"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="1"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="1"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="1"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="1"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="1"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="1"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="1"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="1"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="1"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="1"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="1"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="1"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="1"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="1"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="1"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="1"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="1"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="1"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="1"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="1"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="1"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="1"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="1"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="1"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="1"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="1"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="1"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="1"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="1"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="1"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="1"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="1"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="1"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="1"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="1"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="1"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="1"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="1"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="1"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="1"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="1"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="1"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="1"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B177" s="1"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="1"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="1"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="1"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B181" s="1"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="1"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="1"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="1"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="1"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="1"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="1"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B188" s="1"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B189" s="1"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B190" s="1"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B191" s="1"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="1"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="1"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B194" s="1"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="1"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="1"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="1"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="1"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="1"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="1"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B201" s="1"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="1"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="1"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="1"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="1"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="1"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="1"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="1"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" s="1"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="1"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" s="1"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" s="1"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B213" s="1"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B214" s="1"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" s="1"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B216" s="1"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B217" s="1"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B218" s="1"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" s="1"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B220" s="1"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B221" s="1"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B222" s="1"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" s="1"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="1"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B225" s="1"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B226" s="1"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B227" s="1"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="1"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="1"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B230" s="1"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B231" s="1"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="1"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="1"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="1"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B235" s="1"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"+,Bold"&amp;18Stock Price Data</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b19c134a-14c9-4d4c-af65-c420f94c8cbb}" enabled="0" method="" siteId="{b19c134a-14c9-4d4c-af65-c420f94c8cbb}" removed="1"/>
+</clbl:labelList>
 </file>